--- a/pdf/05_出演者_モデル像.xlsx
+++ b/pdf/05_出演者_モデル像.xlsx
@@ -938,7 +938,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>すれ違う人 二〜四人。知人・友人かエキストラ。うち振り返る一人だけは選ぶ</t>
+          <t>通りすぎる人 二〜四人。知人・友人かエキストラ</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>S5（会社に着いて肩の鞄を掛け直して笑う）が三十秒でいちばん明るい表情になる。ここで自然に笑えるかを必ず見る。S6では振り返られる側なので、横顔・後ろ姿もきれいなこと</t>
+          <t>S5（会社に着いて肩の鞄を掛け直して笑う）が三十秒でいちばん明るい表情になる。ここで自然に笑えるかを必ず見る。巻き戻りのシーンは横移動で追うので、横顔・後ろ姿もきれいなこと</t>
         </is>
       </c>
     </row>
@@ -1256,17 +1256,17 @@
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>すれ違う人（S6）</t>
+          <t>通りすぎる人（S5）</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>二〜四人。うち振り返る一人だけは別に選ぶ</t>
+          <t>二〜四人</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>ロビーを歩くその他大勢なので年齢・性別はばらけてよい。知人・友人に頼むか、エキストラを手配する。ただし振り返り方が不自然だと、ここが一番安っぽくなる。振り返って、一拍見て、また前を向く ── これができる人を一人</t>
+          <t>画面の手前を横切るだけなので年齢・性別はばらけてよい。知人・友人に頼むか、エキストラを手配する。カメラを見ないこと、歩く速さが一定であることの二つだけ守ってもらう ── 通る速さがばらつくと、巻き戻りのテンポが崩れる</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>呼びかけて、振り返ってもらう</t>
+          <t>同じ位置に立ち直してもらう（二回）</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>振り返り方が自然か</t>
+          <t>立ち位置がぶれないか。巻き戻りで同じ画角に戻せるか</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr"/>
